--- a/workspace/spreadsheets/trademark_log.xlsx
+++ b/workspace/spreadsheets/trademark_log.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DSN-A-0001</t>
+          <t>DSN-A-0005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>COLLECTOR STATUS</t>
+          <t>ROTATION STANDARD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>No trademark conflicts found (image not inspected)</t>
+          <t>No trademark conflicts found</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DSN-A-0002</t>
+          <t>DSN-A-0006</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DEADSTOCK ENERGY</t>
+          <t>COLLECTOR STATUS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>No trademark conflicts found (image not inspected)</t>
+          <t>No trademark conflicts found</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DSN-A-0003</t>
+          <t>DSN-A-0007</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NO CREASE CLUB</t>
+          <t>WEAR YOUR PAIRS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>No trademark conflicts found (image not inspected)</t>
+          <t>No trademark conflicts found</t>
         </is>
       </c>
     </row>
@@ -755,17 +755,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DSN-A-0004</t>
+          <t>DSN-B-0001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ROTATION READY</t>
+          <t>Vibes Club</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -795,12 +795,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MANUAL REVIEW</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>No trademark conflicts found (image not inspected)</t>
+          <t>No trademark conflicts found</t>
         </is>
       </c>
     </row>
@@ -812,17 +812,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DSN-A-0005</t>
+          <t>DSN-B-0002</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ROTATION READY V1</t>
+          <t>Daily Culture</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -830,6 +830,11 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>None</t>
@@ -852,111 +857,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Variant — needs TM check</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TM-0006</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DSN-A-0006</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ROTATION READY V2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Variant — needs TM check</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TM-0007</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DSN-A-0007</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ROTATION READY V3</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Variant — needs TM check</t>
+          <t>No trademark conflicts found</t>
         </is>
       </c>
     </row>

--- a/workspace/spreadsheets/trademark_log.xlsx
+++ b/workspace/spreadsheets/trademark_log.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -856,6 +856,1773 @@
         </is>
       </c>
       <c r="M7" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TM-0006</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DSN-A-0008</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DEADSTOCK ENERGY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TM-0007</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DSN-A-0009</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ARCHIVE SERIES</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TM-0008</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DSN-A-0010</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ONE MORE PAIR</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TM-0009</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DSN-A-0011</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODAYS ROTATION</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TM-0010</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DSN-A-0012</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODAYS ROTATION</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>MANUAL REVIEW</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TM-0011</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DSN-A-0013</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WEAR YOUR PAIRS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TM-0012</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DSN-A-0014</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ROTATION ELITE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TM-0013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DSN-A-0015</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DEADSTOCK ENERGY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TM-0014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DSN-A-0016</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ROTATION READY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TM-0015</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DSN-A-0017</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ONE MORE PAIR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TM-0016</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DSN-A-0018</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SNEAKER DAILY</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>MANUAL REVIEW</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TM-0017</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DSN-A-0019</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ROTATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MANUAL REVIEW</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TM-0018</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DSN-A-0020</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>COLLECTORS UNIFORM</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TM-0019</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DSN-A-0021</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SNEAKER ROTATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TM-0020</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DSN-A-0022</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ARCHIVE SERIES</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MANUAL REVIEW</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TM-0021</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DSN-A-0023</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>COLLECTORS UNIFORM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>MANUAL REVIEW</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TM-0022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DSN-A-0024</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PAIR SOCIETY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TM-0023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DSN-A-0025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>COLLECTORS UNIFORM</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TM-0024</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DSN-A-0026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ROTATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MANUAL REVIEW</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TM-0025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DSN-A-0027</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>STREET ROTATION</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TM-0026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DSN-A-0028</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>STREET ROTATION</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>MANUAL REVIEW</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TM-0027</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DSN-A-0029</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>WEAR YOUR PAIRS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TM-0028</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DSN-A-0030</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>COLLECTORS UNIFORM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>MANUAL REVIEW</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TM-0029</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DSN-A-0031</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODAYS ROTATION</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>MANUAL REVIEW</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TM-0030</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DSN-A-0032</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PAIR SOCIETY</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TM-0031</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DSN-A-0033</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>STREET ROTATION</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TM-0032</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DSN-A-0034</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>WEAR YOUR PAIRS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TM-0033</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DSN-A-0035</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>COLLECTORS CLUB</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TM-0034</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DSN-A-0036</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SNEAKER DAILY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TM-0035</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DSN-A-0037</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ROTATION ELITE</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TM-0036</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DSN-A-0038</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODAYS ROTATION</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>No trademark conflicts found</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>No trademark conflicts found</t>
         </is>

--- a/workspace/spreadsheets/trademark_log.xlsx
+++ b/workspace/spreadsheets/trademark_log.xlsx
@@ -2448,7 +2448,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>MANUAL REVIEW</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
